--- a/output/pdf_financials_xlsx/MRC.xlsx
+++ b/output/pdf_financials_xlsx/MRC.xlsx
@@ -1092,10 +1092,10 @@
         <v>0</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.506</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.506</v>
       </c>
     </row>
     <row r="13">
@@ -2062,10 +2062,10 @@
         <v>81.58499999999999</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>298.471</v>
+        <v>297.965</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>240.415</v>
+        <v>239.909</v>
       </c>
     </row>
     <row r="28">
@@ -2182,10 +2182,10 @@
         <v>81.58499999999999</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>298.471</v>
+        <v>297.965</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>240.415</v>
+        <v>239.909</v>
       </c>
     </row>
     <row r="30">
@@ -2242,10 +2242,10 @@
         <v>132.2478157267673</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>505.5488744728061</v>
+        <v>504.6918138857366</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>406.4840645870318</v>
+        <v>405.6285400287429</v>
       </c>
     </row>
     <row r="31">
@@ -2405,34 +2405,34 @@
         <v>123.148</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>93.504</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>241.522</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>134.45</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>110.401</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>123.168</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>173.656</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>111.808</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>116.517</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>140.725</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>184.618</v>
       </c>
     </row>
     <row r="35">
@@ -2525,34 +2525,34 @@
         <v>123.148</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>93.504</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>241.522</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>134.45</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>110.401</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>123.168</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>173.656</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>111.808</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>116.517</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>140.725</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>184.618</v>
       </c>
     </row>
     <row r="37">
@@ -3245,34 +3245,34 @@
         <v>12.074</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>110.293</v>
+        <v>16.789</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>259.129</v>
+        <v>17.607</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>155.532</v>
+        <v>21.082</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>125.952</v>
+        <v>15.551</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>142.264</v>
+        <v>19.096</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>227.008</v>
+        <v>53.352</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>258.967</v>
+        <v>147.159</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>166.361</v>
+        <v>49.844</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>178.331</v>
+        <v>37.606</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>222.063</v>
+        <v>37.445</v>
       </c>
     </row>
     <row r="49">
@@ -7824,34 +7824,34 @@
         <v>0</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-261.141</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-273.435</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-207.283</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-293.648</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-419.757</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-529.745</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-504.404</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-453.996</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-151.601</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-193.979</v>
       </c>
       <c r="Q124" s="3" t="n">
         <v>0</v>
@@ -7884,34 +7884,34 @@
         <v>0</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-261.141</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-273.435</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-207.283</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-293.648</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-419.757</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-529.745</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-504.404</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-453.996</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-151.601</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-193.979</v>
       </c>
       <c r="Q125" s="3" t="n">
         <v>0</v>
@@ -9324,7 +9324,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -34512,7 +34512,11 @@
           <t>Repayment of bank indebtedness</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -62255,7 +62259,7 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
